--- a/AAII_Financials/Quarterly/AKBTY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKBTY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="92">
   <si>
     <t>AKBTY</t>
   </si>
@@ -656,100 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -792,23 +796,26 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
         <v>543700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>493300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>555600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>699300</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -866,8 +873,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -925,8 +935,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -948,8 +961,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1007,8 +1021,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1066,8 +1083,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1110,8 +1130,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1125,8 +1145,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1169,8 +1192,8 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1184,8 +1207,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1204,8 +1230,9 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1248,23 +1275,26 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3">
         <v>341700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>317500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>390500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>524700</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1307,23 +1337,26 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>202000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>175700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>165100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>174700</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1345,8 +1378,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1389,23 +1423,26 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-71400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-61700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-57100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-45000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1448,23 +1485,26 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>139800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>122200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>117800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>137700</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1507,8 +1547,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1522,8 +1562,11 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1566,23 +1609,26 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3">
         <v>130600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>114000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>108000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>129700</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1625,23 +1671,26 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>36800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>27200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>24500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>28800</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1699,8 +1748,11 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1743,23 +1795,26 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3">
         <v>93800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>86800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>83500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>100900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1802,23 +1857,26 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3">
         <v>93800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>86800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>83500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>100900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1876,8 +1934,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1920,8 +1981,8 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -1935,8 +1996,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1994,8 +2058,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2053,8 +2120,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2097,23 +2167,26 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>71400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>61700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>57100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>45000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2156,23 +2229,26 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3">
         <v>93800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>86800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>83500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>100900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2230,8 +2306,11 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2274,87 +2353,93 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3">
         <v>93800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>86800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>83500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>100900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2376,8 +2461,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2399,131 +2485,138 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2439000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2760700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2093700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7560100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3323500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4246100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2123100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2264200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3097300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2609800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2778900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3020800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4122900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3210200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1788200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1685800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1490200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2810900</v>
+      </c>
+      <c r="E42" s="3">
         <v>2889800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2956300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9058100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8206800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2805000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2477200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8791800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9045000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7369000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6551700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3015300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3780600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2877300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>729000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>28400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>530700</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>3300</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -2531,39 +2624,39 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>118400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>55200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13400</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -2576,8 +2669,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2620,8 +2716,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2635,53 +2731,56 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E45" s="3">
         <v>94600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>90600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>488600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>497900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>108200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>113300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1188500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1006300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3211600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2751600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>18800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28300</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -2694,53 +2793,56 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16949000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16475400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17505100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22425400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22155100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18097200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17008700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21029100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23148500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21269400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21375800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14099800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13726500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12211800</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -2753,58 +2855,61 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17760000</v>
+      </c>
+      <c r="E47" s="3">
         <v>16801200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17688500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10863000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11030200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16727400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16670300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9101700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8650100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8394800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8795700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>15018000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13204900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16126000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -2812,126 +2917,135 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1181600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1223900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1258400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1000200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1025400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1063600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1101400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>825500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>839500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>809100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>856100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>617700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>628200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>802100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>177200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>156600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>153100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E49" s="3">
         <v>312000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>265200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>217200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>206300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>192700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>196900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>160500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>153900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>140400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>135400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>116800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>116100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>141600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>35200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>31200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>29700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2989,8 +3103,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3048,67 +3165,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2744200</v>
+      </c>
+      <c r="E52" s="3">
         <v>2357700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2136600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2056100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2001700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1570900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1780300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1924600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1382600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1174300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1152400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1457400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1293600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1637200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3166,67 +3289,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>85998000</v>
+      </c>
+      <c r="E54" s="3">
         <v>81924500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82835200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>77710700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>74955900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75147900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75012400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>70314000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69920700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>63976800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>64412100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>62627400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58573500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>65615300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14119900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13103400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12049400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3248,8 +3377,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3271,53 +3401,54 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>53819300</v>
+      </c>
+      <c r="E57" s="3">
         <v>52122600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50586800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>48744000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>47477400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>46105700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>46159100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>46068300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>44638300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>42403000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43721500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41360800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38591200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>42686300</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -3330,53 +3461,56 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11916500</v>
+      </c>
+      <c r="E58" s="3">
         <v>8995600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11971100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10317700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9869800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12813600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1009200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9799500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11392000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8014700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4032400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6980900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7286000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6740000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -3389,112 +3523,118 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>490900</v>
+      </c>
+      <c r="E59" s="3">
         <v>611700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>352900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>350400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>357400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>309800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>277300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>256300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>417800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>423300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>425900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>287800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>95900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>737800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>33200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>29000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>66269300</v>
+      </c>
+      <c r="E60" s="3">
         <v>61770800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>62949000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>59444600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>57735800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>59260700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>47477900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>56170400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>56487000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>50875800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>48212600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>48663900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>46005500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>50200500</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -3507,126 +3647,135 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8915100</v>
+      </c>
+      <c r="E61" s="3">
         <v>9606500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8603700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7777200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7180800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5586600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17134300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3533900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3694100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3240500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5928700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3904000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3368500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3996300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1296200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1286200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1129300</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3801900</v>
+      </c>
+      <c r="E62" s="3">
         <v>3679000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3737700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3780600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3507600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3875500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3546200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3819900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2965000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3199100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3062200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2915100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2540800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3388600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>77500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>64700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>75600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3684,8 +3833,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3743,8 +3895,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3802,67 +3957,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79037800</v>
+      </c>
+      <c r="E66" s="3">
         <v>75121900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>75616000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>71039900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>68451600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>68744500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>68215900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>63559400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63173200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57397600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57269500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55694400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52069300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>57604500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12262400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11399600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10353700</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3884,8 +4045,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3943,8 +4105,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4002,8 +4167,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4061,8 +4229,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4120,67 +4291,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6025700</v>
+      </c>
+      <c r="E72" s="3">
         <v>5981200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6012900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5771800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5675500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5660600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5863700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5795300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5771500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5501100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5917400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5835700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5351900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6211200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1415400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1295300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1290600</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4238,8 +4415,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4297,8 +4477,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4356,67 +4539,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6960300</v>
+      </c>
+      <c r="E76" s="3">
         <v>6803100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7219700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6670800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6504100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6403200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6796100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6754600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6747400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6579100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7142600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6933000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6504200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8010800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1857500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1703800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1695700</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4474,72 +4663,78 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4582,23 +4777,26 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3">
         <v>93800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>86800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>83500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>100900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4620,67 +4818,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E83" s="3">
         <v>19100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4738,8 +4940,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4797,8 +5002,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4856,8 +5064,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4915,8 +5126,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4974,67 +5188,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4036900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2486000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4541500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4099500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5123200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-77800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2200800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3815500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1649800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-920400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4781200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3918800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3994800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2329100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-43000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-44700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>644400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-124700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5056,67 +5276,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-86100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-108900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-148300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-56200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-64500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-120300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-67800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-52100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-138000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-44500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-57800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-525300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-611900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1032300</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5174,8 +5398,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5233,67 +5460,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-903200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-806700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>26700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-657600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-870200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1392200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-735200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-451400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-734400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1990800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-582000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1863900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1687800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2253800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-351500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-535600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-261900</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5315,29 +5548,30 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3">
         <v>257400</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3">
         <v>167500</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -5345,23 +5579,23 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>307800</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>201500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>195000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -5374,8 +5608,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5433,8 +5670,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5492,8 +5732,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5551,181 +5794,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4669400</v>
+      </c>
+      <c r="E100" s="3">
         <v>3678600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4152800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4057600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5080000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3518500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2861500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3396500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2908300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2809000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5116600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4887800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6906500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4886900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>15500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>184400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-128800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>298700</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>246300</v>
+      </c>
+      <c r="E101" s="3">
         <v>133600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-10200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>149400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>27900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>170000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>174400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>81000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>483500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>69600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>74200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>167400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>264000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>298600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>39500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>64300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>30500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>85000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-181600</v>
+      </c>
+      <c r="E102" s="3">
         <v>425400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-305700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-580500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-667100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2182100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-84700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-721000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>551900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>67700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-72200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-813900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1707400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>373600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-147400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>10500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2900</v>
       </c>
-      <c r="U102" s="3" t="s">
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
